--- a/TESTNapovediPredtekmovanje/SP 2026 - predtekmovanje_Miralem Delic.xlsx
+++ b/TESTNapovediPredtekmovanje/SP 2026 - predtekmovanje_Miralem Delic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\OneDrive\Dokumenti\Nogomet\Stave\SP2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\Documents\SP2026\TESTNapovediPredtekmovanje\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{B413763D-BA23-4F86-8385-4F3120E8DB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4179E83A-BA0F-40BD-AEC3-08754A47C6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -517,7 +517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="157">
   <si>
     <t>PREDTEKMOVANJE</t>
   </si>
@@ -1757,7 +1757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1822,19 +1822,34 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1861,24 +1876,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalno" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2367,9 +2370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema sustava Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2407,7 +2410,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2513,7 +2516,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2655,7 +2658,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2664,71 +2667,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W131"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7421875" customWidth="1"/>
-    <col min="3" max="3" width="9.68359375" customWidth="1"/>
-    <col min="4" max="4" width="15.73828125" customWidth="1"/>
-    <col min="5" max="5" width="6.72265625" customWidth="1"/>
-    <col min="6" max="6" width="2.15234375" customWidth="1"/>
-    <col min="7" max="7" width="15.73828125" customWidth="1"/>
-    <col min="8" max="8" width="6.72265625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="8.875" customWidth="1"/>
-    <col min="10" max="10" width="1.74609375" customWidth="1"/>
-    <col min="11" max="11" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="6" max="6" width="2.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" customWidth="1"/>
+    <col min="10" max="10" width="1.7109375" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-    </row>
-    <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G3" s="37" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+    </row>
+    <row r="3" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="37"/>
-      <c r="I3" s="38" t="s">
+      <c r="H3" s="28"/>
+      <c r="I3" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-    </row>
-    <row r="5" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+    <row r="6" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6">
@@ -2762,8 +2765,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
+    <row r="7" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="24"/>
       <c r="B7" s="6">
         <v>46185</v>
       </c>
@@ -2796,8 +2799,8 @@
       </c>
       <c r="W7" s="3"/>
     </row>
-    <row r="8" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
+    <row r="8" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="24"/>
       <c r="B8" s="6">
         <v>46191</v>
       </c>
@@ -2829,8 +2832,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
+    <row r="9" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="24"/>
       <c r="B9" s="6">
         <v>46192</v>
       </c>
@@ -2862,8 +2865,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
+    <row r="10" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="24"/>
       <c r="B10" s="6">
         <v>46198</v>
       </c>
@@ -2895,8 +2898,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
+    <row r="11" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="24"/>
       <c r="B11" s="6">
         <v>46198</v>
       </c>
@@ -2928,11 +2931,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C12" s="23"/>
     </row>
-    <row r="13" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="6">
@@ -2966,8 +2969,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
+    <row r="14" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="24"/>
       <c r="B14" s="6">
         <v>46186</v>
       </c>
@@ -3000,7 +3003,7 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="6">
         <v>46191</v>
       </c>
@@ -3032,8 +3035,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25"/>
+    <row r="16" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="24"/>
       <c r="B16" s="6">
         <v>46192</v>
       </c>
@@ -3066,7 +3069,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="6">
         <v>46197</v>
       </c>
@@ -3098,8 +3101,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
+    <row r="18" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="24"/>
       <c r="B18" s="6">
         <v>46197</v>
       </c>
@@ -3131,11 +3134,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="23"/>
     </row>
-    <row r="20" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
+    <row r="20" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="24" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="6">
@@ -3169,8 +3172,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
+    <row r="21" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="24"/>
       <c r="B21" s="6">
         <v>46187</v>
       </c>
@@ -3202,8 +3205,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
+    <row r="22" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="24"/>
       <c r="B22" s="6">
         <v>46193</v>
       </c>
@@ -3235,8 +3238,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
+    <row r="23" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="24"/>
       <c r="B23" s="6">
         <v>46193</v>
       </c>
@@ -3268,8 +3271,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
+    <row r="24" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="24"/>
       <c r="B24" s="6">
         <v>46198</v>
       </c>
@@ -3301,8 +3304,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
+    <row r="25" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="24"/>
       <c r="B25" s="6">
         <v>46198</v>
       </c>
@@ -3334,11 +3337,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="23"/>
     </row>
-    <row r="27" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
+    <row r="27" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
         <v>7</v>
       </c>
       <c r="B27" s="6">
@@ -3372,8 +3375,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
+    <row r="28" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="24"/>
       <c r="B28" s="6">
         <v>46187</v>
       </c>
@@ -3405,8 +3408,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
+    <row r="29" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="24"/>
       <c r="B29" s="6">
         <v>46192</v>
       </c>
@@ -3438,8 +3441,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
+    <row r="30" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="24"/>
       <c r="B30" s="6">
         <v>46193</v>
       </c>
@@ -3471,8 +3474,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
+    <row r="31" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="24"/>
       <c r="B31" s="6">
         <v>45469</v>
       </c>
@@ -3504,8 +3507,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25"/>
+    <row r="32" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="24"/>
       <c r="B32" s="6">
         <v>45469</v>
       </c>
@@ -3537,11 +3540,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="23"/>
     </row>
     <row r="34" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="24" t="s">
         <v>8</v>
       </c>
       <c r="B34" s="6">
@@ -3575,8 +3578,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
+    <row r="35" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
       <c r="B35" s="6">
         <v>46188</v>
       </c>
@@ -3608,8 +3611,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
+    <row r="36" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="24"/>
       <c r="B36" s="6">
         <v>46193</v>
       </c>
@@ -3642,7 +3645,7 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="25"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="6">
         <v>45464</v>
       </c>
@@ -3674,8 +3677,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="25"/>
+    <row r="38" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="24"/>
       <c r="B38" s="6">
         <v>46198</v>
       </c>
@@ -3708,7 +3711,7 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="25"/>
+      <c r="A39" s="24"/>
       <c r="B39" s="6">
         <v>46198</v>
       </c>
@@ -3740,11 +3743,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C40" s="23"/>
     </row>
-    <row r="41" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="25" t="s">
+    <row r="41" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="6">
@@ -3778,8 +3781,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
+    <row r="42" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="24"/>
       <c r="B42" s="6">
         <v>46188</v>
       </c>
@@ -3811,8 +3814,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="25"/>
+    <row r="43" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="24"/>
       <c r="B43" s="6">
         <v>46193</v>
       </c>
@@ -3844,8 +3847,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="25"/>
+    <row r="44" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="24"/>
       <c r="B44" s="6">
         <v>45464</v>
       </c>
@@ -3877,8 +3880,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
+    <row r="45" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="24"/>
       <c r="B45" s="6">
         <v>46199</v>
       </c>
@@ -3910,8 +3913,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="25"/>
+    <row r="46" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="24"/>
       <c r="B46" s="6">
         <v>46199</v>
       </c>
@@ -3946,14 +3949,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C47" s="23"/>
       <c r="L47" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="25" t="s">
+    <row r="48" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="24" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="6">
@@ -3987,8 +3990,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="25"/>
+    <row r="49" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="24"/>
       <c r="B49" s="6">
         <v>46189</v>
       </c>
@@ -4020,8 +4023,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="25"/>
+    <row r="50" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="24"/>
       <c r="B50" s="6">
         <v>46194</v>
       </c>
@@ -4053,8 +4056,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="25"/>
+    <row r="51" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="24"/>
       <c r="B51" s="6">
         <v>46195</v>
       </c>
@@ -4086,8 +4089,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="25"/>
+    <row r="52" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="24"/>
       <c r="B52" s="6">
         <v>46200</v>
       </c>
@@ -4119,8 +4122,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="25"/>
+    <row r="53" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="24"/>
       <c r="B53" s="6">
         <v>46200</v>
       </c>
@@ -4152,11 +4155,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C54" s="23"/>
     </row>
-    <row r="55" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="25" t="s">
+    <row r="55" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="24" t="s">
         <v>67</v>
       </c>
       <c r="B55" s="6">
@@ -4190,8 +4193,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="25"/>
+    <row r="56" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="24"/>
       <c r="B56" s="6">
         <v>46189</v>
       </c>
@@ -4223,8 +4226,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="25"/>
+    <row r="57" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="24"/>
       <c r="B57" s="6">
         <v>46194</v>
       </c>
@@ -4256,8 +4259,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="25"/>
+    <row r="58" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="24"/>
       <c r="B58" s="6">
         <v>46195</v>
       </c>
@@ -4289,8 +4292,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="25"/>
+    <row r="59" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="24"/>
       <c r="B59" s="6">
         <v>46200</v>
       </c>
@@ -4322,8 +4325,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="25"/>
+    <row r="60" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="24"/>
       <c r="B60" s="6">
         <v>46200</v>
       </c>
@@ -4355,11 +4358,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C61" s="23"/>
     </row>
-    <row r="62" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="25" t="s">
+    <row r="62" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="24" t="s">
         <v>72</v>
       </c>
       <c r="B62" s="6">
@@ -4393,8 +4396,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="25"/>
+    <row r="63" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="24"/>
       <c r="B63" s="6">
         <v>46190</v>
       </c>
@@ -4426,8 +4429,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="25"/>
+    <row r="64" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="24"/>
       <c r="B64" s="6">
         <v>46195</v>
       </c>
@@ -4459,8 +4462,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="25"/>
+    <row r="65" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="24"/>
       <c r="B65" s="6">
         <v>46196</v>
       </c>
@@ -4492,8 +4495,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="25"/>
+    <row r="66" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="24"/>
       <c r="B66" s="6">
         <v>46199</v>
       </c>
@@ -4525,8 +4528,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="25"/>
+    <row r="67" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="24"/>
       <c r="B67" s="6">
         <v>46199</v>
       </c>
@@ -4558,11 +4561,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C68" s="23"/>
     </row>
     <row r="69" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="25" t="s">
+      <c r="A69" s="24" t="s">
         <v>82</v>
       </c>
       <c r="B69" s="6">
@@ -4596,8 +4599,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="25"/>
+    <row r="70" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="24"/>
       <c r="B70" s="6">
         <v>46190</v>
       </c>
@@ -4629,8 +4632,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="25"/>
+    <row r="71" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="24"/>
       <c r="B71" s="6">
         <v>46195</v>
       </c>
@@ -4663,7 +4666,7 @@
       </c>
     </row>
     <row r="72" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="25"/>
+      <c r="A72" s="24"/>
       <c r="B72" s="6">
         <v>46196</v>
       </c>
@@ -4695,8 +4698,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="25"/>
+    <row r="73" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="24"/>
       <c r="B73" s="6">
         <v>46201</v>
       </c>
@@ -4729,7 +4732,7 @@
       </c>
     </row>
     <row r="74" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="25"/>
+      <c r="A74" s="24"/>
       <c r="B74" s="6">
         <v>46201</v>
       </c>
@@ -4761,11 +4764,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C75" s="23"/>
     </row>
-    <row r="76" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="25" t="s">
+    <row r="76" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="24" t="s">
         <v>83</v>
       </c>
       <c r="B76" s="6">
@@ -4799,8 +4802,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="25"/>
+    <row r="77" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="24"/>
       <c r="B77" s="6">
         <v>46191</v>
       </c>
@@ -4832,8 +4835,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="25"/>
+    <row r="78" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="24"/>
       <c r="B78" s="6">
         <v>46196</v>
       </c>
@@ -4865,8 +4868,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="25"/>
+    <row r="79" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="24"/>
       <c r="B79" s="6">
         <v>46197</v>
       </c>
@@ -4898,8 +4901,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="25"/>
+    <row r="80" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="24"/>
       <c r="B80" s="6">
         <v>46201</v>
       </c>
@@ -4931,8 +4934,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="25"/>
+    <row r="81" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="24"/>
       <c r="B81" s="6">
         <v>46201</v>
       </c>
@@ -4964,11 +4967,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C82" s="23"/>
     </row>
     <row r="83" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="25" t="s">
+      <c r="A83" s="24" t="s">
         <v>84</v>
       </c>
       <c r="B83" s="6">
@@ -5002,8 +5005,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="25"/>
+    <row r="84" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="24"/>
       <c r="B84" s="6">
         <v>46191</v>
       </c>
@@ -5035,8 +5038,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="25"/>
+    <row r="85" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="24"/>
       <c r="B85" s="6">
         <v>46196</v>
       </c>
@@ -5069,7 +5072,7 @@
       </c>
     </row>
     <row r="86" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="25"/>
+      <c r="A86" s="24"/>
       <c r="B86" s="6">
         <v>46197</v>
       </c>
@@ -5101,8 +5104,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="25"/>
+    <row r="87" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="24"/>
       <c r="B87" s="6">
         <v>46200</v>
       </c>
@@ -5135,7 +5138,7 @@
       </c>
     </row>
     <row r="88" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="25"/>
+      <c r="A88" s="24"/>
       <c r="B88" s="6">
         <v>46200</v>
       </c>
@@ -5167,28 +5170,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H89" s="37" t="s">
+    <row r="89" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H89" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="I89" s="37"/>
-      <c r="J89" s="38"/>
-      <c r="K89" s="38"/>
-      <c r="L89" s="38"/>
-      <c r="M89" s="38"/>
-    </row>
-    <row r="90" spans="1:13" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="B90" s="39" t="s">
+      <c r="I89" s="28"/>
+      <c r="J89" s="29"/>
+      <c r="K89" s="29"/>
+      <c r="L89" s="29"/>
+      <c r="M89" s="29"/>
+    </row>
+    <row r="90" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B90" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39"/>
-    </row>
-    <row r="92" spans="1:13" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="B92" s="27" t="s">
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+    </row>
+    <row r="92" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B92" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C92" s="27"/>
+      <c r="C92" s="32"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="G92" s="12" t="s">
@@ -5197,122 +5200,122 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
     </row>
-    <row r="93" spans="1:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B93" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C93" s="26" t="s">
+      <c r="C93" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="D93" s="26"/>
-      <c r="E93" s="26"/>
+      <c r="D93" s="33"/>
+      <c r="E93" s="33"/>
       <c r="F93" s="13">
         <v>2</v>
       </c>
       <c r="G93" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H93" s="26" t="s">
+      <c r="H93" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="I93" s="26"/>
-      <c r="J93" s="26"/>
-      <c r="K93" s="26"/>
-      <c r="L93" s="26"/>
+      <c r="I93" s="33"/>
+      <c r="J93" s="33"/>
+      <c r="K93" s="33"/>
+      <c r="L93" s="33"/>
       <c r="M93" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B94" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C94" s="24" t="s">
+      <c r="C94" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D94" s="24"/>
-      <c r="E94" s="24"/>
+      <c r="D94" s="31"/>
+      <c r="E94" s="31"/>
       <c r="F94" s="13">
         <v>2</v>
       </c>
       <c r="G94" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H94" s="24" t="s">
+      <c r="H94" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="I94" s="24"/>
-      <c r="J94" s="24"/>
-      <c r="K94" s="24"/>
-      <c r="L94" s="24"/>
+      <c r="I94" s="31"/>
+      <c r="J94" s="31"/>
+      <c r="K94" s="31"/>
+      <c r="L94" s="31"/>
       <c r="M94" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C95" s="24" t="s">
+      <c r="C95" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D95" s="24"/>
-      <c r="E95" s="24"/>
+      <c r="D95" s="31"/>
+      <c r="E95" s="31"/>
       <c r="F95" s="13">
         <v>2</v>
       </c>
       <c r="G95" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H95" s="24" t="s">
+      <c r="H95" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I95" s="24"/>
-      <c r="J95" s="24"/>
-      <c r="K95" s="24"/>
-      <c r="L95" s="24"/>
+      <c r="I95" s="31"/>
+      <c r="J95" s="31"/>
+      <c r="K95" s="31"/>
+      <c r="L95" s="31"/>
       <c r="M95" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B96" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C96" s="24" t="s">
+      <c r="C96" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="D96" s="24"/>
-      <c r="E96" s="24"/>
+      <c r="D96" s="31"/>
+      <c r="E96" s="31"/>
       <c r="F96" s="13">
         <v>2</v>
       </c>
       <c r="G96" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H96" s="24" t="s">
+      <c r="H96" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="I96" s="24"/>
-      <c r="J96" s="24"/>
-      <c r="K96" s="24"/>
-      <c r="L96" s="24"/>
+      <c r="I96" s="31"/>
+      <c r="J96" s="31"/>
+      <c r="K96" s="31"/>
+      <c r="L96" s="31"/>
       <c r="M96" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
       <c r="H97" s="3"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" spans="2:13" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="B98" s="27" t="s">
+    <row r="98" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B98" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C98" s="27"/>
+      <c r="C98" s="32"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="G98" s="12" t="s">
@@ -5324,122 +5327,122 @@
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C99" s="26" t="s">
+      <c r="C99" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D99" s="26"/>
-      <c r="E99" s="26"/>
+      <c r="D99" s="33"/>
+      <c r="E99" s="33"/>
       <c r="F99" s="13">
         <v>2</v>
       </c>
       <c r="G99" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H99" s="26" t="s">
+      <c r="H99" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="I99" s="26"/>
-      <c r="J99" s="26"/>
-      <c r="K99" s="26"/>
-      <c r="L99" s="26"/>
+      <c r="I99" s="33"/>
+      <c r="J99" s="33"/>
+      <c r="K99" s="33"/>
+      <c r="L99" s="33"/>
       <c r="M99" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B100" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C100" s="24" t="s">
+      <c r="C100" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="D100" s="24"/>
-      <c r="E100" s="24"/>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
       <c r="F100" s="13">
         <v>2</v>
       </c>
       <c r="G100" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H100" s="26" t="s">
+      <c r="H100" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I100" s="26"/>
-      <c r="J100" s="26"/>
-      <c r="K100" s="26"/>
-      <c r="L100" s="26"/>
+      <c r="I100" s="33"/>
+      <c r="J100" s="33"/>
+      <c r="K100" s="33"/>
+      <c r="L100" s="33"/>
       <c r="M100" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B101" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5" t="s">
+      <c r="C101" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="E101" s="5"/>
+      <c r="D101" s="42"/>
+      <c r="E101" s="42"/>
       <c r="F101" s="13">
         <v>2</v>
       </c>
       <c r="G101" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H101" s="26" t="s">
+      <c r="H101" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="I101" s="26"/>
-      <c r="J101" s="26"/>
-      <c r="K101" s="26"/>
-      <c r="L101" s="26"/>
+      <c r="I101" s="33"/>
+      <c r="J101" s="33"/>
+      <c r="K101" s="33"/>
+      <c r="L101" s="33"/>
       <c r="M101" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B102" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C102" s="24" t="s">
+      <c r="C102" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D102" s="24"/>
-      <c r="E102" s="24"/>
+      <c r="D102" s="31"/>
+      <c r="E102" s="31"/>
       <c r="F102" s="13">
         <v>2</v>
       </c>
       <c r="G102" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H102" s="26" t="s">
+      <c r="H102" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="I102" s="26"/>
-      <c r="J102" s="26"/>
-      <c r="K102" s="26"/>
-      <c r="L102" s="26"/>
+      <c r="I102" s="33"/>
+      <c r="J102" s="33"/>
+      <c r="K102" s="33"/>
+      <c r="L102" s="33"/>
       <c r="M102" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
       <c r="H103" s="3"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
     </row>
-    <row r="104" spans="2:13" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="B104" s="27" t="s">
+    <row r="104" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B104" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C104" s="27"/>
+      <c r="C104" s="32"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="G104" s="12" t="s">
@@ -5451,115 +5454,115 @@
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
     </row>
-    <row r="105" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B105" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C105" s="26" t="s">
+      <c r="C105" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="D105" s="26"/>
-      <c r="E105" s="26"/>
+      <c r="D105" s="33"/>
+      <c r="E105" s="33"/>
       <c r="F105" s="13">
         <v>2</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H105" s="26" t="s">
+      <c r="H105" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="I105" s="26"/>
-      <c r="J105" s="26"/>
-      <c r="K105" s="26"/>
-      <c r="L105" s="26"/>
+      <c r="I105" s="33"/>
+      <c r="J105" s="33"/>
+      <c r="K105" s="33"/>
+      <c r="L105" s="33"/>
       <c r="M105" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B106" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C106" s="24" t="s">
+      <c r="C106" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="D106" s="24"/>
-      <c r="E106" s="24"/>
+      <c r="D106" s="31"/>
+      <c r="E106" s="31"/>
       <c r="F106" s="13">
         <v>2</v>
       </c>
       <c r="G106" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H106" s="26" t="s">
+      <c r="H106" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="I106" s="26"/>
-      <c r="J106" s="26"/>
-      <c r="K106" s="26"/>
-      <c r="L106" s="26"/>
+      <c r="I106" s="33"/>
+      <c r="J106" s="33"/>
+      <c r="K106" s="33"/>
+      <c r="L106" s="33"/>
       <c r="M106" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B107" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C107" s="24" t="s">
+      <c r="C107" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="D107" s="24"/>
-      <c r="E107" s="24"/>
+      <c r="D107" s="31"/>
+      <c r="E107" s="31"/>
       <c r="F107" s="13">
         <v>2</v>
       </c>
       <c r="G107" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H107" s="26" t="s">
+      <c r="H107" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="I107" s="26"/>
-      <c r="J107" s="26"/>
-      <c r="K107" s="26"/>
-      <c r="L107" s="26"/>
+      <c r="I107" s="33"/>
+      <c r="J107" s="33"/>
+      <c r="K107" s="33"/>
+      <c r="L107" s="33"/>
       <c r="M107" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:13" s="10" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B108" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C108" s="24" t="s">
+      <c r="C108" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D108" s="24"/>
-      <c r="E108" s="24"/>
+      <c r="D108" s="31"/>
+      <c r="E108" s="31"/>
       <c r="F108" s="13">
         <v>2</v>
       </c>
       <c r="G108" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H108" s="26" t="s">
+      <c r="H108" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="I108" s="26"/>
-      <c r="J108" s="26"/>
-      <c r="K108" s="26"/>
-      <c r="L108" s="26"/>
+      <c r="I108" s="33"/>
+      <c r="J108" s="33"/>
+      <c r="K108" s="33"/>
+      <c r="L108" s="33"/>
       <c r="M108" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="2:13" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="B110" s="27" t="s">
+    <row r="110" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B110" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C110" s="27"/>
+      <c r="C110" s="32"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
       <c r="G110" s="12" t="s">
@@ -5568,115 +5571,115 @@
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
     </row>
-    <row r="111" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B111" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C111" s="26" t="s">
+      <c r="C111" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D111" s="26"/>
-      <c r="E111" s="26"/>
+      <c r="D111" s="33"/>
+      <c r="E111" s="33"/>
       <c r="F111" s="13">
         <v>2</v>
       </c>
       <c r="G111" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H111" s="26" t="s">
+      <c r="H111" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="I111" s="26"/>
-      <c r="J111" s="26"/>
-      <c r="K111" s="26"/>
-      <c r="L111" s="26"/>
+      <c r="I111" s="33"/>
+      <c r="J111" s="33"/>
+      <c r="K111" s="33"/>
+      <c r="L111" s="33"/>
       <c r="M111" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B112" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C112" s="24" t="s">
+      <c r="C112" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="D112" s="24"/>
-      <c r="E112" s="24"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
       <c r="F112" s="13">
         <v>2</v>
       </c>
       <c r="G112" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H112" s="24" t="s">
+      <c r="H112" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="I112" s="24"/>
-      <c r="J112" s="24"/>
-      <c r="K112" s="24"/>
-      <c r="L112" s="24"/>
+      <c r="I112" s="31"/>
+      <c r="J112" s="31"/>
+      <c r="K112" s="31"/>
+      <c r="L112" s="31"/>
       <c r="M112" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B113" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C113" s="24" t="s">
+      <c r="C113" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="D113" s="24"/>
-      <c r="E113" s="24"/>
+      <c r="D113" s="31"/>
+      <c r="E113" s="31"/>
       <c r="F113" s="13">
         <v>2</v>
       </c>
       <c r="G113" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H113" s="24" t="s">
+      <c r="H113" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="I113" s="24"/>
-      <c r="J113" s="24"/>
-      <c r="K113" s="24"/>
-      <c r="L113" s="24"/>
+      <c r="I113" s="31"/>
+      <c r="J113" s="31"/>
+      <c r="K113" s="31"/>
+      <c r="L113" s="31"/>
       <c r="M113" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B114" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C114" s="24" t="s">
+      <c r="C114" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="D114" s="24"/>
-      <c r="E114" s="24"/>
+      <c r="D114" s="31"/>
+      <c r="E114" s="31"/>
       <c r="F114" s="13">
         <v>2</v>
       </c>
       <c r="G114" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H114" s="24" t="s">
+      <c r="H114" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="I114" s="24"/>
-      <c r="J114" s="24"/>
-      <c r="K114" s="24"/>
-      <c r="L114" s="24"/>
+      <c r="I114" s="31"/>
+      <c r="J114" s="31"/>
+      <c r="K114" s="31"/>
+      <c r="L114" s="31"/>
       <c r="M114" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="2:13" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="B116" s="27" t="s">
+    <row r="116" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B116" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C116" s="27"/>
+      <c r="C116" s="32"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
       <c r="G116" s="12" t="s">
@@ -5685,115 +5688,115 @@
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
     </row>
-    <row r="117" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B117" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C117" s="26" t="s">
+      <c r="C117" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="D117" s="26"/>
-      <c r="E117" s="26"/>
+      <c r="D117" s="33"/>
+      <c r="E117" s="33"/>
       <c r="F117" s="13">
         <v>2</v>
       </c>
       <c r="G117" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H117" s="26" t="s">
+      <c r="H117" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="I117" s="26"/>
-      <c r="J117" s="26"/>
-      <c r="K117" s="26"/>
-      <c r="L117" s="26"/>
+      <c r="I117" s="33"/>
+      <c r="J117" s="33"/>
+      <c r="K117" s="33"/>
+      <c r="L117" s="33"/>
       <c r="M117" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B118" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C118" s="24" t="s">
+      <c r="C118" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D118" s="24"/>
-      <c r="E118" s="24"/>
+      <c r="D118" s="31"/>
+      <c r="E118" s="31"/>
       <c r="F118" s="13">
         <v>2</v>
       </c>
       <c r="G118" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H118" s="24" t="s">
+      <c r="H118" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I118" s="24"/>
-      <c r="J118" s="24"/>
-      <c r="K118" s="24"/>
-      <c r="L118" s="24"/>
+      <c r="I118" s="31"/>
+      <c r="J118" s="31"/>
+      <c r="K118" s="31"/>
+      <c r="L118" s="31"/>
       <c r="M118" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B119" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C119" s="24" t="s">
+      <c r="C119" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="D119" s="24"/>
-      <c r="E119" s="24"/>
+      <c r="D119" s="31"/>
+      <c r="E119" s="31"/>
       <c r="F119" s="13">
         <v>2</v>
       </c>
       <c r="G119" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H119" s="24" t="s">
+      <c r="H119" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="I119" s="24"/>
-      <c r="J119" s="24"/>
-      <c r="K119" s="24"/>
-      <c r="L119" s="24"/>
+      <c r="I119" s="31"/>
+      <c r="J119" s="31"/>
+      <c r="K119" s="31"/>
+      <c r="L119" s="31"/>
       <c r="M119" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B120" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C120" s="24" t="s">
+      <c r="C120" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D120" s="24"/>
-      <c r="E120" s="24"/>
+      <c r="D120" s="31"/>
+      <c r="E120" s="31"/>
       <c r="F120" s="13">
         <v>2</v>
       </c>
       <c r="G120" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H120" s="24" t="s">
+      <c r="H120" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="I120" s="24"/>
-      <c r="J120" s="24"/>
-      <c r="K120" s="24"/>
-      <c r="L120" s="24"/>
+      <c r="I120" s="31"/>
+      <c r="J120" s="31"/>
+      <c r="K120" s="31"/>
+      <c r="L120" s="31"/>
       <c r="M120" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="2:13" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="B122" s="27" t="s">
+    <row r="122" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B122" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C122" s="27"/>
+      <c r="C122" s="32"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="G122" s="12" t="s">
@@ -5802,111 +5805,111 @@
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
     </row>
-    <row r="123" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B123" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C123" s="26" t="s">
+      <c r="C123" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="D123" s="26"/>
-      <c r="E123" s="26"/>
+      <c r="D123" s="33"/>
+      <c r="E123" s="33"/>
       <c r="F123" s="13">
         <v>2</v>
       </c>
       <c r="G123" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H123" s="26" t="s">
+      <c r="H123" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="I123" s="26"/>
-      <c r="J123" s="26"/>
-      <c r="K123" s="26"/>
-      <c r="L123" s="26"/>
+      <c r="I123" s="33"/>
+      <c r="J123" s="33"/>
+      <c r="K123" s="33"/>
+      <c r="L123" s="33"/>
       <c r="M123" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C124" s="24" t="s">
+      <c r="C124" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="D124" s="24"/>
-      <c r="E124" s="24"/>
+      <c r="D124" s="31"/>
+      <c r="E124" s="31"/>
       <c r="F124" s="13">
         <v>2</v>
       </c>
       <c r="G124" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H124" s="24" t="s">
+      <c r="H124" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="I124" s="24"/>
-      <c r="J124" s="24"/>
-      <c r="K124" s="24"/>
-      <c r="L124" s="24"/>
+      <c r="I124" s="31"/>
+      <c r="J124" s="31"/>
+      <c r="K124" s="31"/>
+      <c r="L124" s="31"/>
       <c r="M124" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B125" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C125" s="24" t="s">
+      <c r="C125" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D125" s="24"/>
-      <c r="E125" s="24"/>
+      <c r="D125" s="31"/>
+      <c r="E125" s="31"/>
       <c r="F125" s="13">
         <v>2</v>
       </c>
       <c r="G125" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H125" s="24" t="s">
+      <c r="H125" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="I125" s="24"/>
-      <c r="J125" s="24"/>
-      <c r="K125" s="24"/>
-      <c r="L125" s="24"/>
+      <c r="I125" s="31"/>
+      <c r="J125" s="31"/>
+      <c r="K125" s="31"/>
+      <c r="L125" s="31"/>
       <c r="M125" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B126" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C126" s="24" t="s">
+      <c r="C126" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="D126" s="24"/>
-      <c r="E126" s="24"/>
+      <c r="D126" s="31"/>
+      <c r="E126" s="31"/>
       <c r="F126" s="13">
         <v>2</v>
       </c>
       <c r="G126" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H126" s="24" t="s">
+      <c r="H126" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="I126" s="24"/>
-      <c r="J126" s="24"/>
-      <c r="K126" s="24"/>
-      <c r="L126" s="24"/>
+      <c r="I126" s="31"/>
+      <c r="J126" s="31"/>
+      <c r="K126" s="31"/>
+      <c r="L126" s="31"/>
       <c r="M126" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="2:13" ht="21" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:13" ht="21" x14ac:dyDescent="0.25">
       <c r="B127" s="11"/>
       <c r="C127" s="16"/>
       <c r="D127" s="16"/>
@@ -5920,64 +5923,88 @@
       <c r="L127" s="16"/>
       <c r="M127" s="13"/>
     </row>
-    <row r="129" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="28" t="s">
+    <row r="129" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B129" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C129" s="28"/>
-      <c r="D129" s="28"/>
-      <c r="E129" s="28"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B130" s="28" t="s">
+      <c r="C129" s="27"/>
+      <c r="D129" s="27"/>
+      <c r="E129" s="27"/>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B130" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C130" s="28"/>
-      <c r="D130" s="28"/>
-      <c r="E130" s="28"/>
-      <c r="J130" s="29"/>
-      <c r="K130" s="30"/>
-      <c r="L130" s="31"/>
-    </row>
-    <row r="131" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="28" t="s">
+      <c r="C130" s="27"/>
+      <c r="D130" s="27"/>
+      <c r="E130" s="27"/>
+      <c r="J130" s="34"/>
+      <c r="K130" s="35"/>
+      <c r="L130" s="36"/>
+    </row>
+    <row r="131" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B131" s="28"/>
-      <c r="C131" s="28"/>
-      <c r="D131" s="28"/>
-      <c r="E131" s="28"/>
-      <c r="F131" s="28"/>
-      <c r="G131" s="28"/>
-      <c r="H131" s="35" t="s">
+      <c r="B131" s="27"/>
+      <c r="C131" s="27"/>
+      <c r="D131" s="27"/>
+      <c r="E131" s="27"/>
+      <c r="F131" s="27"/>
+      <c r="G131" s="27"/>
+      <c r="H131" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="I131" s="36"/>
-      <c r="J131" s="32"/>
-      <c r="K131" s="33"/>
-      <c r="L131" s="34"/>
+      <c r="I131" s="41"/>
+      <c r="J131" s="37"/>
+      <c r="K131" s="38"/>
+      <c r="L131" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="J89:M89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
+  <mergeCells count="78">
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C126:E126"/>
+    <mergeCell ref="H126:L126"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A55:A60"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A69:A74"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A83:A88"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="H123:L123"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="H124:L124"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="H125:L125"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="H119:L119"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="H114:L114"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="H120:L120"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="H117:L117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="H118:L118"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="H102:L102"/>
+    <mergeCell ref="H105:L105"/>
+    <mergeCell ref="H106:L106"/>
+    <mergeCell ref="H107:L107"/>
+    <mergeCell ref="H108:L108"/>
+    <mergeCell ref="J130:L131"/>
+    <mergeCell ref="H131:I131"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="H111:L111"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="H112:L112"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="H113:L113"/>
+    <mergeCell ref="B110:C110"/>
     <mergeCell ref="H93:L93"/>
     <mergeCell ref="H94:L94"/>
     <mergeCell ref="H95:L95"/>
@@ -5994,48 +6021,25 @@
     <mergeCell ref="C105:E105"/>
     <mergeCell ref="C99:E99"/>
     <mergeCell ref="C100:E100"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="H102:L102"/>
-    <mergeCell ref="H105:L105"/>
-    <mergeCell ref="H106:L106"/>
-    <mergeCell ref="H107:L107"/>
-    <mergeCell ref="H108:L108"/>
-    <mergeCell ref="J130:L131"/>
-    <mergeCell ref="H131:I131"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="H111:L111"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="H112:L112"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="H113:L113"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="H114:L114"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="H120:L120"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="C117:E117"/>
-    <mergeCell ref="H117:L117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="H118:L118"/>
-    <mergeCell ref="C126:E126"/>
-    <mergeCell ref="H126:L126"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A55:A60"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A69:A74"/>
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A83:A88"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="H123:L123"/>
-    <mergeCell ref="C124:E124"/>
-    <mergeCell ref="H124:L124"/>
-    <mergeCell ref="C125:E125"/>
-    <mergeCell ref="H125:L125"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="H119:L119"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="J89:M89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="86" orientation="portrait" r:id="rId1"/>
